--- a/common/template/document/tabel_teachers_budget_half.xlsx
+++ b/common/template/document/tabel_teachers_budget_half.xlsx
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">  по  ОКПО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                        (должность)                  (подпись)                (расшифровка подписи)</t>
   </si>
   <si>
     <t xml:space="preserve">          Дата</t>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>(первичный - 0; корректирующий - 1, 2 и так далее)</t>
-  </si>
-  <si>
-    <t>Директор</t>
   </si>
   <si>
     <t>Табель № [doc.tabel_num]</t>
@@ -212,9 +206,6 @@
     <t>52603682</t>
   </si>
   <si>
-    <t xml:space="preserve">Исполнитель </t>
-  </si>
-  <si>
     <t>_________</t>
   </si>
   <si>
@@ -276,6 +267,15 @@
   </si>
   <si>
     <t>[a.days.time_total_15;ope=tbs:num]</t>
+  </si>
+  <si>
+    <t>Ответственный исполнитель - Директор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исполнитель - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        (должность)               (подпись)             (расшифровка подписи)</t>
   </si>
 </sst>
 </file>
@@ -365,7 +365,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -522,32 +522,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -752,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -767,19 +741,16 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -809,23 +780,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -835,7 +806,7 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -850,6 +821,40 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -871,44 +876,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1283,13 +1257,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT605"/>
+  <dimension ref="A1:AT606"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="6.140625" customWidth="1"/>
     <col min="3" max="3" width="5.7109375" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="19" width="3.42578125" customWidth="1"/>
     <col min="20" max="20" width="6.140625" customWidth="1"/>
     <col min="21" max="36" width="3.42578125" customWidth="1"/>
@@ -1297,310 +1271,310 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="AG1" s="65"/>
-      <c r="AH1" s="65"/>
-      <c r="AI1" s="65"/>
-      <c r="AJ1" s="65"/>
-      <c r="AK1" s="65"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
+      <c r="AI1" s="56"/>
+      <c r="AJ1" s="56"/>
+      <c r="AK1" s="56"/>
     </row>
     <row r="2" spans="1:46" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H2" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
+      <c r="H2" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
     </row>
     <row r="3" spans="1:46" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="AI3" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ3" s="28"/>
-      <c r="AK3" s="29"/>
+      <c r="E3" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="AI3" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="26"/>
     </row>
     <row r="4" spans="1:46" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AE4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI4" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="68"/>
+        <v>18</v>
+      </c>
+      <c r="AI4" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="59"/>
     </row>
     <row r="5" spans="1:46" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G5" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="60"/>
-      <c r="W5" s="60"/>
-      <c r="X5" s="60"/>
-      <c r="Y5" s="60"/>
+      <c r="G5" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="68"/>
+      <c r="Y5" s="68"/>
       <c r="AF5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI5" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ5" s="72"/>
-      <c r="AK5" s="73"/>
+        <v>6</v>
+      </c>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="54"/>
+      <c r="AK5" s="55"/>
     </row>
     <row r="6" spans="1:46" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="D6" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="70"/>
-      <c r="Y6" s="70"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="70"/>
-      <c r="AB6" s="70"/>
+      <c r="A6" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="D6" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="61"/>
+      <c r="Z6" s="61"/>
+      <c r="AA6" s="61"/>
+      <c r="AB6" s="61"/>
       <c r="AF6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AK6" s="9"/>
     </row>
     <row r="7" spans="1:46" s="1" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="66"/>
+      <c r="U7" s="66"/>
+      <c r="V7" s="66"/>
+      <c r="W7" s="66"/>
+      <c r="X7" s="66"/>
+      <c r="Y7" s="66"/>
+      <c r="Z7" s="66"/>
+      <c r="AA7" s="66"/>
+      <c r="AB7" s="66"/>
+      <c r="AI7" s="11"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="13"/>
+    </row>
+    <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="D8" s="72">
+        <v>0</v>
+      </c>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="72"/>
+      <c r="Y8" s="72"/>
+      <c r="Z8" s="72"/>
+      <c r="AA8" s="72"/>
+      <c r="AB8" s="72"/>
+      <c r="AC8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="58"/>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="58"/>
-      <c r="AI7" s="14"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="16"/>
-    </row>
-    <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="D8" s="64">
-        <v>0</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="64"/>
-      <c r="W8" s="64"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="64"/>
-      <c r="Z8" s="64"/>
-      <c r="AA8" s="64"/>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="1" t="s">
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="13"/>
+    </row>
+    <row r="9" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI8" s="14"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="16"/>
-    </row>
-    <row r="9" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G9" s="13"/>
-      <c r="K9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE9" s="17"/>
-      <c r="AI9" s="10"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="12"/>
+      <c r="AE9" s="14"/>
+      <c r="AI9" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="55"/>
     </row>
     <row r="10" spans="1:46" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
-      <c r="AE10" s="23"/>
-      <c r="AF10" s="23"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="23"/>
-      <c r="AJ10" s="23"/>
-      <c r="AK10" s="23"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="20"/>
     </row>
     <row r="11" spans="1:46" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="40" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
-      <c r="AH11" s="22"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="22"/>
-      <c r="AK11" s="24"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="19"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="21"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
@@ -1612,14 +1586,14 @@
       <c r="AT11" s="1"/>
     </row>
     <row r="12" spans="1:46" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>45</v>
+      <c r="B12" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>43</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
@@ -1638,7 +1612,7 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="4"/>
@@ -1657,7 +1631,7 @@
       <c r="AI12" s="4"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -1670,11 +1644,11 @@
       <c r="AT12" s="1"/>
     </row>
     <row r="13" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1692,7 +1666,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -1710,8 +1684,8 @@
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
-      <c r="AK13" s="20" t="s">
-        <v>10</v>
+      <c r="AK13" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -1724,9 +1698,9 @@
       <c r="AT13" s="1"/>
     </row>
     <row r="14" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,7 +1750,7 @@
         <v>15</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U14" s="3">
         <v>16</v>
@@ -1826,8 +1800,8 @@
       <c r="AJ14" s="3">
         <v>31</v>
       </c>
-      <c r="AK14" s="20" t="s">
-        <v>13</v>
+      <c r="AK14" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
@@ -1840,11 +1814,11 @@
       <c r="AT14" s="1"/>
     </row>
     <row r="15" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1880,7 +1854,7 @@
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
-      <c r="AK15" s="20" t="s">
+      <c r="AK15" s="17" t="s">
         <v>0</v>
       </c>
       <c r="AL15" s="1"/>
@@ -1894,9 +1868,9 @@
       <c r="AT15" s="1"/>
     </row>
     <row r="16" spans="1:46" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1914,7 +1888,7 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -1932,8 +1906,8 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
-      <c r="AK16" s="20" t="s">
-        <v>14</v>
+      <c r="AK16" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
@@ -1946,9 +1920,9 @@
       <c r="AT16" s="1"/>
     </row>
     <row r="17" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1965,8 +1939,8 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="21" t="s">
-        <v>15</v>
+      <c r="T17" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -1985,7 +1959,7 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
@@ -2004,109 +1978,109 @@
       <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="21">
         <v>3</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="21">
         <v>4</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="21">
         <v>5</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="21">
         <v>6</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="21">
         <v>7</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="21">
         <v>8</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="21">
         <v>9</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="21">
         <v>10</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="21">
         <v>11</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="21">
         <v>12</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="21">
         <v>13</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="21">
         <v>14</v>
       </c>
-      <c r="O18" s="24">
+      <c r="O18" s="21">
         <v>15</v>
       </c>
-      <c r="P18" s="24">
+      <c r="P18" s="21">
         <v>16</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="Q18" s="21">
         <v>17</v>
       </c>
-      <c r="R18" s="24">
+      <c r="R18" s="21">
         <v>18</v>
       </c>
-      <c r="S18" s="24">
+      <c r="S18" s="21">
         <v>19</v>
       </c>
-      <c r="T18" s="24">
+      <c r="T18" s="21">
         <v>20</v>
       </c>
-      <c r="U18" s="24">
+      <c r="U18" s="21">
         <v>21</v>
       </c>
-      <c r="V18" s="24">
+      <c r="V18" s="21">
         <v>22</v>
       </c>
-      <c r="W18" s="24">
+      <c r="W18" s="21">
         <v>23</v>
       </c>
-      <c r="X18" s="24">
+      <c r="X18" s="21">
         <v>24</v>
       </c>
-      <c r="Y18" s="24">
+      <c r="Y18" s="21">
         <v>25</v>
       </c>
-      <c r="Z18" s="24">
+      <c r="Z18" s="21">
         <v>26</v>
       </c>
-      <c r="AA18" s="24">
+      <c r="AA18" s="21">
         <v>27</v>
       </c>
-      <c r="AB18" s="24">
+      <c r="AB18" s="21">
         <v>28</v>
       </c>
-      <c r="AC18" s="24">
+      <c r="AC18" s="21">
         <v>29</v>
       </c>
-      <c r="AD18" s="24">
+      <c r="AD18" s="21">
         <v>30</v>
       </c>
-      <c r="AE18" s="24">
+      <c r="AE18" s="21">
         <v>31</v>
       </c>
-      <c r="AF18" s="24">
+      <c r="AF18" s="21">
         <v>32</v>
       </c>
-      <c r="AG18" s="24">
+      <c r="AG18" s="21">
         <v>33</v>
       </c>
-      <c r="AH18" s="24">
+      <c r="AH18" s="21">
         <v>34</v>
       </c>
-      <c r="AI18" s="24">
+      <c r="AI18" s="21">
         <v>35</v>
       </c>
-      <c r="AJ18" s="24">
+      <c r="AJ18" s="21">
         <v>36</v>
       </c>
-      <c r="AK18" s="24">
+      <c r="AK18" s="21">
         <v>37</v>
       </c>
       <c r="AL18" s="1"/>
@@ -2119,341 +2093,447 @@
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
     </row>
-    <row r="19" spans="1:46" s="47" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="43" t="s">
+    <row r="19" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="43" t="s">
+      <c r="E19" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="O19" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="P19" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="R19" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="S19" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="T19" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="U19" s="52"/>
+      <c r="V19" s="52"/>
+      <c r="W19" s="52"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="52"/>
+      <c r="AA19" s="52"/>
+      <c r="AB19" s="52"/>
+      <c r="AC19" s="52"/>
+      <c r="AD19" s="52"/>
+      <c r="AE19" s="52"/>
+      <c r="AF19" s="52"/>
+      <c r="AG19" s="52"/>
+      <c r="AH19" s="52"/>
+      <c r="AI19" s="52"/>
+      <c r="AJ19" s="52"/>
+      <c r="AK19" s="52"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="1"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1"/>
+      <c r="AS19" s="1"/>
+      <c r="AT19" s="1"/>
+    </row>
+    <row r="20" spans="1:46" s="44" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="H20" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="I20" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="J20" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="K20" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="44" t="s">
+      <c r="L20" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="44" t="s">
+      <c r="M20" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="L19" s="44" t="s">
+      <c r="N20" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M19" s="44" t="s">
+      <c r="O20" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="N19" s="44" t="s">
+      <c r="P20" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="O19" s="44" t="s">
+      <c r="Q20" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="P19" s="44" t="s">
+      <c r="R20" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Q19" s="44" t="s">
+      <c r="S20" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="R19" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="S19" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="T19" s="45">
+      <c r="T20" s="42">
         <f ca="1">COUNTIF(INDIRECT(ADDRESS(ROW(),COLUMN()-15))   : INDIRECT(ADDRESS(ROW(),COLUMN()-1)), "Ф" )</f>
         <v>0</v>
       </c>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="44"/>
-      <c r="AF19" s="44"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="44"/>
-      <c r="AI19" s="44"/>
-      <c r="AJ19" s="44"/>
-      <c r="AK19" s="46"/>
-    </row>
-    <row r="20" spans="1:46" s="47" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="K20" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="L20" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="M20" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="N20" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="P20" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q20" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="R20" s="43" t="s">
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="41"/>
+      <c r="AK20" s="43"/>
+    </row>
+    <row r="21" spans="1:46" s="44" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="50" t="e">
+        <f ca="1">SUMPRODUCT((T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))*ISODD(ROW(T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="49"/>
+      <c r="AF21" s="49"/>
+      <c r="AG21" s="49"/>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49"/>
+      <c r="AJ21" s="49"/>
+      <c r="AK21" s="50"/>
+    </row>
+    <row r="22" spans="1:46" s="51" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+    </row>
+    <row r="23" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q23" s="28"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="30"/>
+    </row>
+    <row r="24" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="S20" s="43" t="s">
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22"/>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="22"/>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="22"/>
+      <c r="AK24" s="33"/>
+    </row>
+    <row r="25" spans="1:46" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="31"/>
+      <c r="AK25" s="33"/>
+    </row>
+    <row r="26" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="E26" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="T20" s="50" t="s">
+      <c r="U26" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y26" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC26" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="AK26" s="33"/>
+    </row>
+    <row r="27" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E27" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27" s="31"/>
+      <c r="S27" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="43"/>
-      <c r="AH20" s="43"/>
-      <c r="AI20" s="43"/>
-      <c r="AJ20" s="43"/>
-      <c r="AK20" s="50"/>
-    </row>
-    <row r="21" spans="1:46" s="54" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="53" t="e">
-        <f ca="1">SUMPRODUCT(( T20                    : INDIRECT(ADDRESS(ROW()-1,COLUMN())))*ISEVEN(ROW( T20                    : INDIRECT(ADDRESS(ROW()-1,COLUMN())))))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U21" s="52"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="52"/>
-      <c r="X21" s="52"/>
-      <c r="Y21" s="52"/>
-      <c r="Z21" s="52"/>
-      <c r="AA21" s="52"/>
-      <c r="AB21" s="52"/>
-      <c r="AC21" s="52"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="52"/>
-      <c r="AF21" s="52"/>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="52"/>
-      <c r="AI21" s="52"/>
-      <c r="AJ21" s="52"/>
-      <c r="AK21" s="53"/>
-    </row>
-    <row r="22" spans="1:46" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q23" s="31"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="32"/>
-      <c r="AB23" s="32"/>
-      <c r="AC23" s="32"/>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="32"/>
-      <c r="AJ23" s="32"/>
-      <c r="AK23" s="33"/>
-    </row>
-    <row r="24" spans="1:46" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="E24" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="Q24" s="34"/>
-      <c r="T24" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK24" s="36"/>
-    </row>
-    <row r="25" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="34"/>
-      <c r="AK25" s="36"/>
-    </row>
-    <row r="26" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
+      <c r="AK27" s="33"/>
+    </row>
+    <row r="28" spans="1:46" s="22" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q28" s="31"/>
+      <c r="AK28" s="33"/>
+    </row>
+    <row r="29" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q29" s="31"/>
+      <c r="R29" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="E26" s="26" t="s">
+      <c r="AK29" s="33"/>
+    </row>
+    <row r="30" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="U26" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y26" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC26" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK26" s="36"/>
-    </row>
-    <row r="27" spans="1:46" s="25" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E27" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" s="34"/>
-      <c r="S27" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK27" s="36"/>
-    </row>
-    <row r="28" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q28" s="34"/>
-      <c r="AK28" s="36"/>
-    </row>
-    <row r="29" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q29" s="34"/>
-      <c r="R29" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK29" s="36"/>
-    </row>
-    <row r="30" spans="1:46" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="38"/>
-      <c r="V30" s="38"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="38"/>
-      <c r="Z30" s="38"/>
-      <c r="AA30" s="38"/>
-      <c r="AB30" s="38"/>
-      <c r="AC30" s="38"/>
-      <c r="AD30" s="38"/>
-      <c r="AE30" s="38"/>
-      <c r="AF30" s="38"/>
-      <c r="AG30" s="38"/>
-      <c r="AH30" s="38"/>
-      <c r="AI30" s="38"/>
-      <c r="AJ30" s="38"/>
-      <c r="AK30" s="39"/>
-    </row>
-    <row r="31" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="35"/>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="35"/>
+      <c r="AF30" s="35"/>
+      <c r="AG30" s="35"/>
+      <c r="AH30" s="35"/>
+      <c r="AI30" s="35"/>
+      <c r="AJ30" s="35"/>
+      <c r="AK30" s="36"/>
+    </row>
+    <row r="31" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+      <c r="X31"/>
+      <c r="Y31"/>
+      <c r="Z31"/>
+      <c r="AA31"/>
+      <c r="AB31"/>
+      <c r="AC31"/>
+      <c r="AD31"/>
+      <c r="AE31"/>
+      <c r="AF31"/>
+      <c r="AG31"/>
+      <c r="AH31"/>
+      <c r="AI31"/>
+      <c r="AJ31"/>
+      <c r="AK31"/>
+    </row>
+    <row r="32" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="378" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
@@ -2492,15 +2572,6 @@
       <c r="AI378" s="1"/>
       <c r="AJ378" s="1"/>
       <c r="AK378" s="1"/>
-      <c r="AL378" s="1"/>
-      <c r="AM378" s="1"/>
-      <c r="AN378" s="1"/>
-      <c r="AO378" s="1"/>
-      <c r="AP378" s="1"/>
-      <c r="AQ378" s="1"/>
-      <c r="AR378" s="1"/>
-      <c r="AS378" s="1"/>
-      <c r="AT378" s="1"/>
     </row>
     <row r="379" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
@@ -13398,14 +13469,19 @@
       <c r="AS605" s="1"/>
       <c r="AT605" s="1"/>
     </row>
+    <row r="606" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="AL606" s="1"/>
+      <c r="AM606" s="1"/>
+      <c r="AN606" s="1"/>
+      <c r="AO606" s="1"/>
+      <c r="AP606" s="1"/>
+      <c r="AQ606" s="1"/>
+      <c r="AR606" s="1"/>
+      <c r="AS606" s="1"/>
+      <c r="AT606" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="H2:U2"/>
-    <mergeCell ref="D6:AB6"/>
-    <mergeCell ref="AI5:AK5"/>
-    <mergeCell ref="E3:Y3"/>
+  <mergeCells count="15">
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="C12:C17"/>
     <mergeCell ref="D7:AB7"/>
@@ -13414,6 +13490,13 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D8:AB8"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="H2:U2"/>
+    <mergeCell ref="D6:AB6"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="E3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/common/template/document/tabel_teachers_budget_half.xlsx
+++ b/common/template/document/tabel_teachers_budget_half.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>явок</t>
   </si>
@@ -113,9 +113,6 @@
     <t>[doc.org_briefname]</t>
   </si>
   <si>
-    <t>[doc.departments]</t>
-  </si>
-  <si>
     <t>(подпись)</t>
   </si>
   <si>
@@ -206,9 +203,6 @@
     <t>52603682</t>
   </si>
   <si>
-    <t>_________</t>
-  </si>
-  <si>
     <t>[doc.doc_accountant_post]</t>
   </si>
   <si>
@@ -272,10 +266,22 @@
     <t>Ответственный исполнитель - Директор</t>
   </si>
   <si>
-    <t xml:space="preserve">Исполнитель - </t>
+    <t>Педагогические работники</t>
   </si>
   <si>
-    <t xml:space="preserve">                        (должность)               (подпись)             (расшифровка подписи)</t>
+    <t>первичный</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>(расшифровка подписи)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исполнитель </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                             (должность)                  (подпись)                (расшифровка подписи)</t>
   </si>
 </sst>
 </file>
@@ -285,7 +291,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -340,12 +346,6 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <name val="Arial Cyr"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <u/>
       <sz val="8"/>
       <name val="Arial Cyr"/>
       <charset val="204"/>
@@ -726,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -795,7 +795,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -822,6 +821,36 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -855,36 +884,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1271,54 +1272,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="56"/>
-      <c r="AJ1" s="56"/>
-      <c r="AK1" s="56"/>
+      <c r="AG1" s="65"/>
+      <c r="AH1" s="65"/>
+      <c r="AI1" s="65"/>
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
     </row>
     <row r="2" spans="1:46" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
     </row>
     <row r="3" spans="1:46" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="62"/>
-      <c r="U3" s="62"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
+      <c r="E3" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
       <c r="AI3" s="24" t="s">
         <v>16</v>
       </c>
@@ -1329,79 +1330,79 @@
       <c r="AE4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AI4" s="57" t="s">
+      <c r="AI4" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="AJ4" s="58"/>
-      <c r="AK4" s="59"/>
+      <c r="AJ4" s="67"/>
+      <c r="AK4" s="68"/>
     </row>
     <row r="5" spans="1:46" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
       <c r="AF5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="54"/>
-      <c r="AK5" s="55"/>
+      <c r="AI5" s="62"/>
+      <c r="AJ5" s="63"/>
+      <c r="AK5" s="64"/>
     </row>
     <row r="6" spans="1:46" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="D6" s="61" t="s">
+      <c r="B6" s="58"/>
+      <c r="D6" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="61"/>
-      <c r="W6" s="61"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="61"/>
-      <c r="Z6" s="61"/>
-      <c r="AA6" s="61"/>
-      <c r="AB6" s="61"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="70"/>
+      <c r="Z6" s="70"/>
+      <c r="AA6" s="70"/>
+      <c r="AB6" s="70"/>
       <c r="AF6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AK6" s="9"/>
     </row>
@@ -1409,75 +1410,77 @@
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-      <c r="T7" s="66"/>
-      <c r="U7" s="66"/>
-      <c r="V7" s="66"/>
-      <c r="W7" s="66"/>
-      <c r="X7" s="66"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="66"/>
-      <c r="AA7" s="66"/>
-      <c r="AB7" s="66"/>
+      <c r="D7" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
       <c r="AI7" s="11"/>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="13"/>
     </row>
     <row r="8" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="D8" s="72">
-        <v>0</v>
-      </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72"/>
-      <c r="X8" s="72"/>
-      <c r="Y8" s="72"/>
-      <c r="Z8" s="72"/>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
+      <c r="B8" s="58"/>
+      <c r="D8" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="61"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="61"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="61"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="61"/>
+      <c r="Z8" s="61"/>
+      <c r="AA8" s="61"/>
+      <c r="AB8" s="61"/>
       <c r="AC8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="AI8" s="11"/>
       <c r="AJ8" s="12"/>
-      <c r="AK8" s="13"/>
+      <c r="AK8" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="9" spans="1:46" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G9" s="10"/>
@@ -1488,11 +1491,11 @@
         <v>24</v>
       </c>
       <c r="AE9" s="14"/>
-      <c r="AI9" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="55"/>
+      <c r="AI9" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ9" s="63"/>
+      <c r="AK9" s="64"/>
     </row>
     <row r="10" spans="1:46" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20"/>
@@ -1535,10 +1538,10 @@
     </row>
     <row r="11" spans="1:46" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="15"/>
       <c r="E11" s="27"/>
       <c r="F11" s="19"/>
@@ -1589,11 +1592,11 @@
       <c r="A12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="52" t="s">
         <v>42</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>43</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
@@ -1647,8 +1650,8 @@
       <c r="A13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1699,8 +1702,8 @@
     </row>
     <row r="14" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1815,8 +1818,8 @@
     </row>
     <row r="15" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
@@ -1869,8 +1872,8 @@
     </row>
     <row r="16" spans="1:46" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1921,8 +1924,8 @@
     </row>
     <row r="17" spans="1:46" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2094,83 +2097,83 @@
       <c r="AT18" s="1"/>
     </row>
     <row r="19" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="40" t="s">
+      <c r="A19" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="D19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="H19" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="I19" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="J19" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="K19" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="L19" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="40" t="s">
+      <c r="M19" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="L19" s="40" t="s">
+      <c r="N19" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="M19" s="40" t="s">
+      <c r="O19" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="N19" s="40" t="s">
+      <c r="P19" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="O19" s="40" t="s">
+      <c r="Q19" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="P19" s="40" t="s">
+      <c r="R19" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="Q19" s="40" t="s">
+      <c r="S19" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="R19" s="40" t="s">
+      <c r="T19" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="S19" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="T19" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="U19" s="52"/>
-      <c r="V19" s="52"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="52"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="52"/>
-      <c r="AG19" s="52"/>
-      <c r="AH19" s="52"/>
-      <c r="AI19" s="52"/>
-      <c r="AJ19" s="52"/>
-      <c r="AK19" s="52"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="51"/>
+      <c r="W19" s="51"/>
+      <c r="X19" s="51"/>
+      <c r="Y19" s="51"/>
+      <c r="Z19" s="51"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="51"/>
+      <c r="AC19" s="51"/>
+      <c r="AD19" s="51"/>
+      <c r="AE19" s="51"/>
+      <c r="AF19" s="51"/>
+      <c r="AG19" s="51"/>
+      <c r="AH19" s="51"/>
+      <c r="AI19" s="51"/>
+      <c r="AJ19" s="51"/>
+      <c r="AK19" s="51"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
@@ -2181,125 +2184,125 @@
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
     </row>
-    <row r="20" spans="1:46" s="44" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="41" t="s">
+    <row r="20" spans="1:46" s="43" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="G20" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="H20" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="41" t="s">
+      <c r="I20" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="41" t="s">
+      <c r="J20" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="41" t="s">
+      <c r="K20" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="41" t="s">
+      <c r="L20" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="L20" s="41" t="s">
+      <c r="M20" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="M20" s="41" t="s">
+      <c r="N20" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="N20" s="41" t="s">
+      <c r="O20" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="O20" s="41" t="s">
+      <c r="P20" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="P20" s="41" t="s">
+      <c r="Q20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="Q20" s="41" t="s">
+      <c r="R20" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="R20" s="41" t="s">
+      <c r="S20" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="S20" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="T20" s="42">
+      <c r="T20" s="41">
         <f ca="1">COUNTIF(INDIRECT(ADDRESS(ROW(),COLUMN()-15))   : INDIRECT(ADDRESS(ROW(),COLUMN()-1)), "Ф" )</f>
         <v>0</v>
       </c>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="41"/>
-      <c r="AK20" s="43"/>
-    </row>
-    <row r="21" spans="1:46" s="44" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="49"/>
-      <c r="R21" s="49"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="50" t="e">
-        <f ca="1">SUMPRODUCT((T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))*ISODD(ROW(T19                          : INDIRECT(ADDRESS( ROW()-1,COLUMN())))))</f>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="40"/>
+      <c r="Y20" s="40"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="40"/>
+      <c r="AB20" s="40"/>
+      <c r="AC20" s="40"/>
+      <c r="AD20" s="40"/>
+      <c r="AE20" s="40"/>
+      <c r="AF20" s="40"/>
+      <c r="AG20" s="40"/>
+      <c r="AH20" s="40"/>
+      <c r="AI20" s="40"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="42"/>
+    </row>
+    <row r="21" spans="1:46" s="43" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="49" t="e">
+        <f ca="1">SUMPRODUCT((T19                           : INDIRECT(ADDRESS( ROW()-1,COLUMN())))*ISODD(ROW(T19                           : INDIRECT(ADDRESS( ROW()-1,COLUMN())))))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U21" s="49"/>
-      <c r="V21" s="49"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="49"/>
-      <c r="Z21" s="49"/>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="49"/>
-      <c r="AF21" s="49"/>
-      <c r="AG21" s="49"/>
-      <c r="AH21" s="49"/>
-      <c r="AI21" s="49"/>
-      <c r="AJ21" s="49"/>
-      <c r="AK21" s="50"/>
-    </row>
-    <row r="22" spans="1:46" s="51" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="48"/>
+      <c r="X21" s="48"/>
+      <c r="Y21" s="48"/>
+      <c r="Z21" s="48"/>
+      <c r="AA21" s="48"/>
+      <c r="AB21" s="48"/>
+      <c r="AC21" s="48"/>
+      <c r="AD21" s="48"/>
+      <c r="AE21" s="48"/>
+      <c r="AF21" s="48"/>
+      <c r="AG21" s="48"/>
+      <c r="AH21" s="48"/>
+      <c r="AI21" s="48"/>
+      <c r="AJ21" s="48"/>
+      <c r="AK21" s="49"/>
+    </row>
+    <row r="22" spans="1:46" s="50" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -2362,25 +2365,25 @@
       <c r="AK23" s="30"/>
     </row>
     <row r="24" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23" t="s">
-        <v>31</v>
-      </c>
+      <c r="A24" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
+      <c r="H24" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
       <c r="P24" s="22"/>
       <c r="Q24" s="31"/>
       <c r="R24" s="22"/>
@@ -2405,55 +2408,74 @@
       <c r="AI24" s="22"/>
       <c r="AJ24" s="22"/>
       <c r="AK24" s="33"/>
+      <c r="AL24" s="22"/>
     </row>
     <row r="25" spans="1:46" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="D25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
       <c r="Q25" s="31"/>
       <c r="AK25" s="33"/>
     </row>
     <row r="26" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="E26" s="23" t="s">
+      <c r="A26" s="72" t="s">
         <v>32</v>
       </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
+      <c r="H26" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
       <c r="Q26" s="31"/>
       <c r="R26" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="U26" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y26" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="U26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y26" s="23"/>
+      <c r="Z26" s="23"/>
+      <c r="AA26" s="23"/>
+      <c r="AB26" s="23"/>
+      <c r="AC26" s="23"/>
+      <c r="AD26" s="23"/>
+      <c r="AE26" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="AC26" s="38" t="s">
-        <v>62</v>
-      </c>
       <c r="AK26" s="33"/>
     </row>
     <row r="27" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E27" s="22" t="s">
-        <v>30</v>
-      </c>
+      <c r="D27" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="72"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="72"/>
       <c r="Q27" s="31"/>
       <c r="S27" s="22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK27" s="33"/>
     </row>
@@ -2464,14 +2486,15 @@
     <row r="29" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q29" s="31"/>
       <c r="R29" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AK29" s="33"/>
     </row>
     <row r="30" spans="1:46" s="22" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>34</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H30"/>
       <c r="Q30" s="34"/>
       <c r="R30" s="35"/>
       <c r="S30" s="35"/>
@@ -13482,6 +13505,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="H2:U2"/>
+    <mergeCell ref="D6:AB6"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="E3:Y3"/>
     <mergeCell ref="B12:B17"/>
     <mergeCell ref="C12:C17"/>
     <mergeCell ref="D7:AB7"/>
@@ -13490,13 +13520,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D8:AB8"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="AI9:AK9"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="H2:U2"/>
-    <mergeCell ref="D6:AB6"/>
-    <mergeCell ref="AI5:AK5"/>
-    <mergeCell ref="E3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
